--- a/2026년 과학원 연구과제(안정동위원소)/오염원 정답지 관련/(260416) 오염원 정답지 실험(MixSIAR, EMMTE 결과 포함).xlsx
+++ b/2026년 과학원 연구과제(안정동위원소)/오염원 정답지 관련/(260416) 오염원 정답지 실험(MixSIAR, EMMTE 결과 포함).xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\업무관련자료\2026년 업무자료\2026~2027년 조사연구사업 관련(안정동위원소, 국가 수질측정망 적용)\2026년 연구사업 관련\2026년 오염원 추적 연구단 관련\오염원 정답지 작성 관련\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026~2027년 연구사업 관련\2026년\2026년 오염원 추적 연구단 관련\오염원 정답지 관련\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7D1039-AD4C-4338-9DAB-8F16BDF95AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="30720" windowHeight="13215" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="kendall plot(정답지 실험결과)" sheetId="1" r:id="rId1"/>
+    <sheet name="260416 실험" sheetId="1" r:id="rId1"/>
     <sheet name="MixSIAR 결과" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="25">
   <si>
     <t>No</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -174,7 +175,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
@@ -450,13 +451,13 @@
     <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="1"/>
+    <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -517,32 +518,49 @@
             </c:spPr>
           </c:marker>
           <c:xVal>
-            <c:numRef>
-              <c:f>'kendall plot(정답지 실험결과)'!$D$2:$D$55</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="54"/>
+            <c:strRef>
+              <c:f>'260416 실험'!$D$2:$D$55</c:f>
+              <c:strCache>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>15.17</c:v>
+                  <c:v>15.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-6.85</c:v>
+                  <c:v>-6.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.13</c:v>
+                  <c:v>15.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.14</c:v>
+                  <c:v>13.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.01</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>11.0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15N</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-6.9</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>15.1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>13.1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>11.0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'kendall plot(정답지 실험결과)'!$E$2:$E$55</c:f>
+              <c:f>'260416 실험'!$E$2:$E$55</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="54"/>
@@ -553,6 +571,18 @@
                   <c:v>-1.33</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>1.89</c:v>
+                </c:pt>
+                <c:pt idx="25" formatCode="@">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-3.24</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-1.33</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>1.89</c:v>
                 </c:pt>
               </c:numCache>
@@ -591,32 +621,49 @@
             </c:spPr>
           </c:marker>
           <c:xVal>
-            <c:numRef>
-              <c:f>'kendall plot(정답지 실험결과)'!$D$2:$D$55</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="54"/>
+            <c:strRef>
+              <c:f>'260416 실험'!$D$2:$D$55</c:f>
+              <c:strCache>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>15.17</c:v>
+                  <c:v>15.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-6.85</c:v>
+                  <c:v>-6.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.13</c:v>
+                  <c:v>15.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.14</c:v>
+                  <c:v>13.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.01</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>11.0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15N</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-6.9</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>15.1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>13.1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>11.0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'kendall plot(정답지 실험결과)'!$F$2:$F$55</c:f>
+              <c:f>'260416 실험'!$F$2:$F$55</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="54"/>
@@ -624,6 +671,15 @@
                   <c:v>-3.82</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>11.02</c:v>
+                </c:pt>
+                <c:pt idx="25" formatCode="@">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-3.82</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>11.02</c:v>
                 </c:pt>
               </c:numCache>
@@ -662,35 +718,67 @@
             </c:spPr>
           </c:marker>
           <c:xVal>
-            <c:numRef>
-              <c:f>'kendall plot(정답지 실험결과)'!$D$2:$D$55</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="54"/>
+            <c:strRef>
+              <c:f>'260416 실험'!$D$2:$D$55</c:f>
+              <c:strCache>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>15.17</c:v>
+                  <c:v>15.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-6.85</c:v>
+                  <c:v>-6.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.13</c:v>
+                  <c:v>15.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.14</c:v>
+                  <c:v>13.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.01</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>11.0</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>15N</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>15.2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-6.9</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>15.1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>13.1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>11.0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'kendall plot(정답지 실험결과)'!$G$2:$G$55</c:f>
+              <c:f>'260416 실험'!$G$2:$G$55</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="54"/>
+                <c:pt idx="26">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="@">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>92.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>89.3</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>23.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2743,7 +2831,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2944,7 +3032,7 @@
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -2952,7 +3040,7 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -2960,7 +3048,7 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
@@ -2968,7 +3056,7 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
@@ -2976,7 +3064,7 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -2984,7 +3072,7 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -2992,7 +3080,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -3000,7 +3088,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -3008,7 +3096,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -3016,54 +3104,216 @@
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
+    <row r="27" spans="1:13" ht="27" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="8">
+        <v>1.042</v>
+      </c>
+      <c r="D28" s="9">
+        <v>15.17</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9">
+        <v>-3.82</v>
+      </c>
+      <c r="G28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28"/>
+      <c r="I28"/>
+      <c r="J28"/>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28"/>
+      <c r="M28"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="9">
+        <v>-6.85</v>
+      </c>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9">
+        <v>11.02</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29"/>
+      <c r="K29" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="9">
+        <v>15.13</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-3.24</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30">
+        <v>92.7</v>
+      </c>
+      <c r="H30">
+        <v>7.3</v>
+      </c>
+      <c r="I30">
+        <f>SUM(G30:H30)</f>
+        <v>100</v>
+      </c>
+      <c r="J30"/>
+      <c r="K30">
+        <v>96.78</v>
+      </c>
+      <c r="L30">
+        <v>3.22</v>
+      </c>
+      <c r="M30">
+        <f>SUM(K30:L30)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="9">
+        <v>13.14</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-1.33</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31">
+        <v>89.3</v>
+      </c>
+      <c r="H31">
+        <v>10.7</v>
+      </c>
+      <c r="I31">
+        <f t="shared" ref="I31:I32" si="0">SUM(G31:H31)</f>
+        <v>100</v>
+      </c>
+      <c r="J31"/>
+      <c r="K31">
+        <v>83.95</v>
+      </c>
+      <c r="L31">
+        <v>16.05</v>
+      </c>
+      <c r="M31">
+        <f t="shared" ref="M31:M32" si="1">SUM(K31:L31)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="8"/>
+      <c r="D32" s="9">
+        <v>11.01</v>
+      </c>
+      <c r="E32" s="9">
+        <v>1.89</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32">
+        <v>23.5</v>
+      </c>
+      <c r="H32">
+        <v>76.5</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J32"/>
+      <c r="K32">
+        <v>65.36</v>
+      </c>
+      <c r="L32">
+        <v>34.64</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
@@ -3235,7 +3485,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:M26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
